--- a/Versão5/ABNT/Ontologia_NBR15965_3E.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_3E.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E63D8F8-3CEA-4536-BFF7-CCF3D1EA0AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{663ADC25-C329-4085-80A7-EDE7C058D684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18593" uniqueCount="1950">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18593" uniqueCount="1951">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -5912,12 +5912,6 @@
     <t>NBR.Temáticas</t>
   </si>
   <si>
-    <t>[ OST_Materials ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ IfcMaterial ] </t>
-  </si>
-  <si>
     <t>[ - ]</t>
   </si>
   <si>
@@ -5933,16 +5927,25 @@
     <t>[ OST_Rooms : OST_MEPSpaces : OST_MEPSystemZone ]</t>
   </si>
   <si>
-    <t>[ IfcSpace ]</t>
-  </si>
-  <si>
-    <t>[ IfcProperty ]</t>
-  </si>
-  <si>
     <t>[ OST_Sheets : OST_TitleBlocks : OST_Revisions : OST_RevisionNumberingSequences ]</t>
   </si>
   <si>
     <t>[ IfcAnnotation ]</t>
+  </si>
+  <si>
+    <t>[ OST_Materials : OST_MaterialTags ]</t>
+  </si>
+  <si>
+    <t>[ IfcMaterial : IfcText : IfcLabel : IfcMaterialRelationship ]</t>
+  </si>
+  <si>
+    <t>[ BuiltInParameter ]</t>
+  </si>
+  <si>
+    <t>[ IfcProperty : IfcIdentifier : IfcText ]</t>
+  </si>
+  <si>
+    <t>[ IfcSpace : IfcRelSpaceBoundary : IfcSpaceType : IfcSpaceTypeEnum ]</t>
   </si>
 </sst>
 </file>
@@ -6515,7 +6518,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{7762E94B-0EF8-4169-A51C-F9B49B760C57}"/>
   </cellStyles>
-  <dxfs count="65">
+  <dxfs count="66">
     <dxf>
       <font>
         <b val="0"/>
@@ -6589,6 +6592,13 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
@@ -8192,33 +8202,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y722" headerRowCount="0" totalsRowShown="0" headerRowDxfId="64" dataDxfId="62" headerRowBorderDxfId="63" tableBorderDxfId="61" totalsRowBorderDxfId="60">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y722" headerRowCount="0" totalsRowShown="0" headerRowDxfId="65" dataDxfId="63" headerRowBorderDxfId="64" tableBorderDxfId="62" totalsRowBorderDxfId="61">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="59" dataDxfId="58"/>
-    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="57" dataDxfId="56"/>
-    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="55" dataDxfId="54"/>
-    <tableColumn id="11" xr3:uid="{7E912914-9569-4822-984C-7A1AF4C10EAE}" name="Coluna8" headerRowDxfId="53" dataDxfId="52"/>
-    <tableColumn id="10" xr3:uid="{CDA30AA3-6CC0-4D6B-AA3D-8201E7A1023C}" name="Coluna7" headerRowDxfId="51" dataDxfId="50"/>
-    <tableColumn id="26" xr3:uid="{14DEC38B-5BC0-4C90-8E5C-1E35ACBA832D}" name="Coluna19" headerRowDxfId="49" dataDxfId="48"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="47" dataDxfId="46"/>
-    <tableColumn id="4" xr3:uid="{CA2BF8F3-B237-40DC-9F32-AE22CDD6890C}" name="Coluna1" headerRowDxfId="45" dataDxfId="44"/>
-    <tableColumn id="5" xr3:uid="{36C796DC-6C7E-4B41-87B9-9FCF9B82EE70}" name="Coluna2" headerRowDxfId="43" dataDxfId="42"/>
-    <tableColumn id="6" xr3:uid="{56BA1A67-ABAC-4289-86BE-471F0E0A5E64}" name="Coluna3" headerRowDxfId="41" dataDxfId="40"/>
-    <tableColumn id="7" xr3:uid="{359EFFF9-0CB6-41EE-8805-290113822D31}" name="Coluna4" headerRowDxfId="39" dataDxfId="38"/>
-    <tableColumn id="24" xr3:uid="{4E625920-945F-4868-96CA-1E9865A82F1B}" name="Coluna21" headerRowDxfId="37" dataDxfId="36"/>
-    <tableColumn id="12" xr3:uid="{A045FBDA-3EB3-48DF-8B48-041D1CD62621}" name="Coluna20" headerRowDxfId="35" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{482EF924-06FF-4A9E-8F53-CA8519E91C6A}" name="Coluna5" headerRowDxfId="33" dataDxfId="32"/>
-    <tableColumn id="9" xr3:uid="{B772DC13-CA24-463F-93C9-F7821EBCC314}" name="Coluna6" headerRowDxfId="31" dataDxfId="30"/>
-    <tableColumn id="14" xr3:uid="{7C5E1ACB-9144-4A9B-BE11-C1C1B7337842}" name="Coluna9" headerRowDxfId="29" dataDxfId="28"/>
-    <tableColumn id="15" xr3:uid="{D82361B2-6609-4711-ABE0-509E1D365618}" name="Coluna10" headerRowDxfId="27" dataDxfId="26"/>
-    <tableColumn id="16" xr3:uid="{FA89BFC3-A470-4C5B-8EDE-3888662AD6DF}" name="Coluna11" headerRowDxfId="25" dataDxfId="24"/>
-    <tableColumn id="17" xr3:uid="{7461A7D5-3F34-4122-877D-BA99287C1DDC}" name="Coluna12" headerRowDxfId="23" dataDxfId="22"/>
-    <tableColumn id="18" xr3:uid="{90564319-2742-4584-A135-64808AD65253}" name="Coluna13" headerRowDxfId="21" dataDxfId="20"/>
-    <tableColumn id="19" xr3:uid="{5AD80C80-D087-4B6C-8A72-CF0A5AA8E9C5}" name="Coluna14" headerRowDxfId="19" dataDxfId="18"/>
-    <tableColumn id="20" xr3:uid="{ADCE9408-1D25-4A86-896A-DC3040DCC77A}" name="Coluna15" headerRowDxfId="17" dataDxfId="16"/>
-    <tableColumn id="21" xr3:uid="{E9E06793-AB89-4B33-B62D-508D99B8AE8B}" name="Coluna16" headerRowDxfId="15" dataDxfId="14"/>
-    <tableColumn id="22" xr3:uid="{E1409F83-40B1-4B25-89A1-45CE84A94FDA}" name="Coluna17" headerRowDxfId="13" dataDxfId="12"/>
-    <tableColumn id="23" xr3:uid="{FFF4EFB8-C5DF-42B3-8EE2-618A27B1C442}" name="Coluna18" headerRowDxfId="11" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="60" dataDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="58" dataDxfId="57"/>
+    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="56" dataDxfId="55"/>
+    <tableColumn id="11" xr3:uid="{7E912914-9569-4822-984C-7A1AF4C10EAE}" name="Coluna8" headerRowDxfId="54" dataDxfId="53"/>
+    <tableColumn id="10" xr3:uid="{CDA30AA3-6CC0-4D6B-AA3D-8201E7A1023C}" name="Coluna7" headerRowDxfId="52" dataDxfId="51"/>
+    <tableColumn id="26" xr3:uid="{14DEC38B-5BC0-4C90-8E5C-1E35ACBA832D}" name="Coluna19" headerRowDxfId="50" dataDxfId="49"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="48" dataDxfId="47"/>
+    <tableColumn id="4" xr3:uid="{CA2BF8F3-B237-40DC-9F32-AE22CDD6890C}" name="Coluna1" headerRowDxfId="46" dataDxfId="45"/>
+    <tableColumn id="5" xr3:uid="{36C796DC-6C7E-4B41-87B9-9FCF9B82EE70}" name="Coluna2" headerRowDxfId="44" dataDxfId="43"/>
+    <tableColumn id="6" xr3:uid="{56BA1A67-ABAC-4289-86BE-471F0E0A5E64}" name="Coluna3" headerRowDxfId="42" dataDxfId="41"/>
+    <tableColumn id="7" xr3:uid="{359EFFF9-0CB6-41EE-8805-290113822D31}" name="Coluna4" headerRowDxfId="40" dataDxfId="39"/>
+    <tableColumn id="24" xr3:uid="{4E625920-945F-4868-96CA-1E9865A82F1B}" name="Coluna21" headerRowDxfId="38" dataDxfId="37"/>
+    <tableColumn id="12" xr3:uid="{A045FBDA-3EB3-48DF-8B48-041D1CD62621}" name="Coluna20" headerRowDxfId="36" dataDxfId="35"/>
+    <tableColumn id="8" xr3:uid="{482EF924-06FF-4A9E-8F53-CA8519E91C6A}" name="Coluna5" headerRowDxfId="34" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{B772DC13-CA24-463F-93C9-F7821EBCC314}" name="Coluna6" headerRowDxfId="32" dataDxfId="31"/>
+    <tableColumn id="14" xr3:uid="{7C5E1ACB-9144-4A9B-BE11-C1C1B7337842}" name="Coluna9" headerRowDxfId="30" dataDxfId="29"/>
+    <tableColumn id="15" xr3:uid="{D82361B2-6609-4711-ABE0-509E1D365618}" name="Coluna10" headerRowDxfId="28" dataDxfId="27"/>
+    <tableColumn id="16" xr3:uid="{FA89BFC3-A470-4C5B-8EDE-3888662AD6DF}" name="Coluna11" headerRowDxfId="26" dataDxfId="25"/>
+    <tableColumn id="17" xr3:uid="{7461A7D5-3F34-4122-877D-BA99287C1DDC}" name="Coluna12" headerRowDxfId="24" dataDxfId="23"/>
+    <tableColumn id="18" xr3:uid="{90564319-2742-4584-A135-64808AD65253}" name="Coluna13" headerRowDxfId="22" dataDxfId="21"/>
+    <tableColumn id="19" xr3:uid="{5AD80C80-D087-4B6C-8A72-CF0A5AA8E9C5}" name="Coluna14" headerRowDxfId="20" dataDxfId="19"/>
+    <tableColumn id="20" xr3:uid="{ADCE9408-1D25-4A86-896A-DC3040DCC77A}" name="Coluna15" headerRowDxfId="18" dataDxfId="17"/>
+    <tableColumn id="21" xr3:uid="{E9E06793-AB89-4B33-B62D-508D99B8AE8B}" name="Coluna16" headerRowDxfId="16" dataDxfId="15"/>
+    <tableColumn id="22" xr3:uid="{E1409F83-40B1-4B25-89A1-45CE84A94FDA}" name="Coluna17" headerRowDxfId="14" dataDxfId="13"/>
+    <tableColumn id="23" xr3:uid="{FFF4EFB8-C5DF-42B3-8EE2-618A27B1C442}" name="Coluna18" headerRowDxfId="12" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -8543,14 +8553,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6150FAF1-0727-432D-9C9B-B6DB6881C7C4}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="65.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="20.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>3</v>
       </c>
@@ -8561,7 +8571,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>728</v>
       </c>
@@ -8572,7 +8582,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
         <v>729</v>
       </c>
@@ -8583,7 +8593,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>4</v>
       </c>
@@ -8594,7 +8604,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>5</v>
       </c>
@@ -8605,7 +8615,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>6</v>
       </c>
@@ -8616,7 +8626,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>7</v>
       </c>
@@ -8627,7 +8637,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>8</v>
       </c>
@@ -8638,7 +8648,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>732</v>
       </c>
@@ -8649,7 +8659,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>734</v>
       </c>
@@ -8660,7 +8670,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>735</v>
       </c>
@@ -8671,7 +8681,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>9</v>
       </c>
@@ -8682,7 +8692,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>736</v>
       </c>
@@ -8693,7 +8703,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>737</v>
       </c>
@@ -8704,7 +8714,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>738</v>
       </c>
@@ -8715,7 +8725,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>739</v>
       </c>
@@ -8726,7 +8736,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>11</v>
       </c>
@@ -8737,19 +8747,19 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>740</v>
       </c>
       <c r="B18" s="19">
         <f ca="1">NOW()</f>
-        <v>46244.497569212966</v>
+        <v>46249.324005671297</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>1527</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
         <v>1537</v>
       </c>
@@ -8760,7 +8770,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>1531</v>
       </c>
@@ -8772,7 +8782,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>1538</v>
       </c>
@@ -8784,7 +8794,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>727</v>
       </c>
@@ -8795,7 +8805,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>741</v>
       </c>
@@ -8806,7 +8816,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
         <v>1465</v>
       </c>
@@ -8817,7 +8827,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
         <v>1467</v>
       </c>
@@ -8828,7 +8838,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>1523</v>
       </c>
@@ -8839,7 +8849,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>1910</v>
       </c>
@@ -8850,7 +8860,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="16" t="s">
         <v>1912</v>
       </c>
@@ -8861,7 +8871,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="16" t="s">
         <v>1914</v>
       </c>
@@ -8872,7 +8882,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="16" t="s">
         <v>1916</v>
       </c>
@@ -8883,7 +8893,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="16" t="s">
         <v>1918</v>
       </c>
@@ -8894,7 +8904,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="16" t="s">
         <v>1920</v>
       </c>
@@ -8905,7 +8915,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="16" t="s">
         <v>1922</v>
       </c>
@@ -8916,7 +8926,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="16" t="s">
         <v>1924</v>
       </c>
@@ -8927,7 +8937,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="16" t="s">
         <v>1926</v>
       </c>
@@ -8938,7 +8948,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="16" t="s">
         <v>1928</v>
       </c>
@@ -8949,7 +8959,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" s="64" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="16" t="s">
         <v>1930</v>
       </c>
@@ -8960,7 +8970,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="18" t="s">
         <v>1932</v>
       </c>
@@ -8971,7 +8981,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="68" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" s="68" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="16" t="s">
         <v>1934</v>
       </c>
@@ -8998,34 +9008,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E67B40A7-0299-43C5-B399-F7F9056DD3F6}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA61"/>
-  <sheetFormatPr defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" customWidth="1"/>
-    <col min="2" max="2" width="6.83203125" style="33" customWidth="1"/>
-    <col min="3" max="3" width="7.5" style="33" customWidth="1"/>
-    <col min="4" max="4" width="10" style="33" customWidth="1"/>
-    <col min="5" max="5" width="9.6640625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="16.33203125" style="33" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8.6640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7" customWidth="1"/>
-    <col min="13" max="13" width="9.33203125" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
-    <col min="15" max="15" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="62" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="70" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.83203125" style="33" customWidth="1"/>
-    <col min="19" max="19" width="8.33203125" customWidth="1"/>
-    <col min="20" max="20" width="10" customWidth="1"/>
-    <col min="21" max="21" width="10.1640625" customWidth="1"/>
-    <col min="22" max="22" width="9.6640625" customWidth="1"/>
-    <col min="23" max="23" width="8.6640625" style="33" customWidth="1"/>
-    <col min="24" max="24" width="44.33203125" customWidth="1"/>
-    <col min="25" max="25" width="8.5" customWidth="1"/>
-    <col min="26" max="26" width="11.1640625" customWidth="1"/>
-    <col min="27" max="27" width="64.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5" style="33" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.296875" style="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.09765625" style="33" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.19921875" style="33" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5" style="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8.3984375" style="33" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.09765625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="62.8984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="65.09765625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.796875" style="33" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.296875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.09765625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.8984375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.5" style="33" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="31.09765625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="57.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>1471</v>
       </c>
@@ -9108,7 +9118,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="50">
         <v>2</v>
       </c>
@@ -9187,10 +9197,10 @@
         <v>Key-ABNT-2</v>
       </c>
       <c r="X2" s="37" t="s">
-        <v>1939</v>
+        <v>1946</v>
       </c>
       <c r="Y2" s="37" t="s">
-        <v>1940</v>
+        <v>1947</v>
       </c>
       <c r="Z2" s="37" t="s">
         <v>1548</v>
@@ -9199,7 +9209,7 @@
         <v>1873</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="50">
         <v>3</v>
       </c>
@@ -9278,10 +9288,10 @@
         <v>Key-ABNT-3</v>
       </c>
       <c r="X3" s="37" t="s">
-        <v>1941</v>
+        <v>1948</v>
       </c>
       <c r="Y3" s="37" t="s">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="Z3" s="37" t="s">
         <v>1549</v>
@@ -9290,7 +9300,7 @@
         <v>1876</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="50">
         <v>4</v>
       </c>
@@ -9369,10 +9379,10 @@
         <v>Key-ABNT-4</v>
       </c>
       <c r="X4" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y4" s="37" t="s">
-        <v>1942</v>
+        <v>1940</v>
       </c>
       <c r="Z4" s="37" t="s">
         <v>1550</v>
@@ -9381,7 +9391,7 @@
         <v>1879</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="50">
         <v>5</v>
       </c>
@@ -9460,10 +9470,10 @@
         <v>Key-ABNT-5</v>
       </c>
       <c r="X5" s="37" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="Y5" s="37" t="s">
-        <v>1944</v>
+        <v>1942</v>
       </c>
       <c r="Z5" s="37" t="s">
         <v>1551</v>
@@ -9472,7 +9482,7 @@
         <v>1882</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="50">
         <v>6</v>
       </c>
@@ -9551,10 +9561,10 @@
         <v>Key-ABNT-6</v>
       </c>
       <c r="X6" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y6" s="37" t="s">
-        <v>1942</v>
+        <v>1940</v>
       </c>
       <c r="Z6" s="37" t="s">
         <v>1552</v>
@@ -9563,7 +9573,7 @@
         <v>1885</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="50">
         <v>7</v>
       </c>
@@ -9642,10 +9652,10 @@
         <v>Key-ABNT-7</v>
       </c>
       <c r="X7" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y7" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z7" s="37" t="s">
         <v>1553</v>
@@ -9654,7 +9664,7 @@
         <v>1888</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="50">
         <v>8</v>
       </c>
@@ -9733,10 +9743,10 @@
         <v>Key-ABNT-8</v>
       </c>
       <c r="X8" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y8" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z8" s="37" t="s">
         <v>1554</v>
@@ -9745,7 +9755,7 @@
         <v>1891</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="50">
         <v>9</v>
       </c>
@@ -9824,10 +9834,10 @@
         <v>Key-ABNT-9</v>
       </c>
       <c r="X9" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y9" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z9" s="37" t="s">
         <v>1555</v>
@@ -9836,7 +9846,7 @@
         <v>1894</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="50">
         <v>10</v>
       </c>
@@ -9915,10 +9925,10 @@
         <v>Key-ABNT-10</v>
       </c>
       <c r="X10" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y10" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z10" s="37" t="s">
         <v>1521</v>
@@ -9927,7 +9937,7 @@
         <v>1897</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="50">
         <v>11</v>
       </c>
@@ -10006,10 +10016,10 @@
         <v>Key-ABNT-11</v>
       </c>
       <c r="X11" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y11" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z11" s="37" t="s">
         <v>1556</v>
@@ -10018,7 +10028,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="50">
         <v>12</v>
       </c>
@@ -10097,10 +10107,10 @@
         <v>Key-ABNT-12</v>
       </c>
       <c r="X12" s="37" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="Y12" s="37" t="s">
-        <v>1946</v>
+        <v>1950</v>
       </c>
       <c r="Z12" s="37" t="s">
         <v>1557</v>
@@ -10109,7 +10119,7 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="50">
         <v>13</v>
       </c>
@@ -10188,10 +10198,10 @@
         <v>Key-ABNT-13</v>
       </c>
       <c r="X13" s="37" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="Y13" s="37" t="s">
-        <v>1946</v>
+        <v>1950</v>
       </c>
       <c r="Z13" s="37" t="s">
         <v>1558</v>
@@ -10200,7 +10210,7 @@
         <v>1906</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="50">
         <v>14</v>
       </c>
@@ -10279,10 +10289,10 @@
         <v>Key-ABNT-14</v>
       </c>
       <c r="X14" s="69" t="s">
-        <v>1948</v>
+        <v>1944</v>
       </c>
       <c r="Y14" s="70" t="s">
-        <v>1949</v>
+        <v>1945</v>
       </c>
       <c r="Z14" s="37" t="s">
         <v>1559</v>
@@ -10291,7 +10301,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="50">
         <v>15</v>
       </c>
@@ -10370,10 +10380,10 @@
         <v>Key-ABNT-15</v>
       </c>
       <c r="X15" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y15" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z15" s="54" t="s">
         <v>1668</v>
@@ -10382,7 +10392,7 @@
         <v>1776</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="50">
         <v>16</v>
       </c>
@@ -10461,10 +10471,10 @@
         <v>Key-ABNT-16</v>
       </c>
       <c r="X16" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y16" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z16" s="54" t="s">
         <v>1669</v>
@@ -10473,7 +10483,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="50">
         <v>17</v>
       </c>
@@ -10552,10 +10562,10 @@
         <v>Key-ABNT-17</v>
       </c>
       <c r="X17" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y17" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z17" s="54" t="s">
         <v>1670</v>
@@ -10564,7 +10574,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="50">
         <v>18</v>
       </c>
@@ -10643,10 +10653,10 @@
         <v>Key-ABNT-18</v>
       </c>
       <c r="X18" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y18" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z18" s="54" t="s">
         <v>1671</v>
@@ -10655,7 +10665,7 @@
         <v>1779</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="50">
         <v>19</v>
       </c>
@@ -10734,10 +10744,10 @@
         <v>Key-ABNT-19</v>
       </c>
       <c r="X19" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y19" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z19" s="54" t="s">
         <v>1672</v>
@@ -10746,7 +10756,7 @@
         <v>1780</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="50">
         <v>20</v>
       </c>
@@ -10825,10 +10835,10 @@
         <v>Key-ABNT-20</v>
       </c>
       <c r="X20" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y20" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z20" s="54" t="s">
         <v>1673</v>
@@ -10837,7 +10847,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="50">
         <v>21</v>
       </c>
@@ -10916,10 +10926,10 @@
         <v>Key-ABNT-21</v>
       </c>
       <c r="X21" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y21" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z21" s="54" t="s">
         <v>1674</v>
@@ -10928,7 +10938,7 @@
         <v>1782</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="50">
         <v>22</v>
       </c>
@@ -11007,10 +11017,10 @@
         <v>Key-ABNT-22</v>
       </c>
       <c r="X22" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y22" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z22" s="54" t="s">
         <v>1675</v>
@@ -11019,7 +11029,7 @@
         <v>1783</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="50">
         <v>23</v>
       </c>
@@ -11098,10 +11108,10 @@
         <v>Key-ABNT-23</v>
       </c>
       <c r="X23" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y23" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z23" s="54" t="s">
         <v>1676</v>
@@ -11110,7 +11120,7 @@
         <v>1784</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="50">
         <v>24</v>
       </c>
@@ -11189,10 +11199,10 @@
         <v>Key-ABNT-24</v>
       </c>
       <c r="X24" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y24" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z24" s="54" t="s">
         <v>1677</v>
@@ -11201,7 +11211,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="50">
         <v>25</v>
       </c>
@@ -11280,10 +11290,10 @@
         <v>Key-ABNT-25</v>
       </c>
       <c r="X25" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y25" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z25" s="54" t="s">
         <v>1678</v>
@@ -11292,7 +11302,7 @@
         <v>1786</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="50">
         <v>26</v>
       </c>
@@ -11371,10 +11381,10 @@
         <v>Key-ABNT-26</v>
       </c>
       <c r="X26" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y26" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z26" s="54" t="s">
         <v>1679</v>
@@ -11383,7 +11393,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="50">
         <v>27</v>
       </c>
@@ -11462,10 +11472,10 @@
         <v>Key-ABNT-27</v>
       </c>
       <c r="X27" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y27" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z27" s="54" t="s">
         <v>1680</v>
@@ -11474,7 +11484,7 @@
         <v>1788</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="50">
         <v>28</v>
       </c>
@@ -11553,10 +11563,10 @@
         <v>Key-ABNT-28</v>
       </c>
       <c r="X28" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y28" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z28" s="54" t="s">
         <v>1681</v>
@@ -11565,7 +11575,7 @@
         <v>1789</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="50">
         <v>29</v>
       </c>
@@ -11644,10 +11654,10 @@
         <v>Key-ABNT-29</v>
       </c>
       <c r="X29" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y29" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z29" s="54" t="s">
         <v>1682</v>
@@ -11656,7 +11666,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="50">
         <v>30</v>
       </c>
@@ -11735,10 +11745,10 @@
         <v>Key-ABNT-30</v>
       </c>
       <c r="X30" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y30" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z30" s="54" t="s">
         <v>1683</v>
@@ -11747,7 +11757,7 @@
         <v>1791</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="50">
         <v>31</v>
       </c>
@@ -11826,10 +11836,10 @@
         <v>Key-ABNT-31</v>
       </c>
       <c r="X31" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y31" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z31" s="54" t="s">
         <v>1684</v>
@@ -11838,7 +11848,7 @@
         <v>1792</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="50">
         <v>32</v>
       </c>
@@ -11917,10 +11927,10 @@
         <v>Key-ABNT-32</v>
       </c>
       <c r="X32" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y32" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z32" s="54" t="s">
         <v>1685</v>
@@ -11929,7 +11939,7 @@
         <v>1793</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="50">
         <v>33</v>
       </c>
@@ -12008,10 +12018,10 @@
         <v>Key-ABNT-33</v>
       </c>
       <c r="X33" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y33" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z33" s="54" t="s">
         <v>1686</v>
@@ -12020,7 +12030,7 @@
         <v>1794</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="50">
         <v>34</v>
       </c>
@@ -12099,10 +12109,10 @@
         <v>Key-ABNT-34</v>
       </c>
       <c r="X34" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y34" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z34" s="54" t="s">
         <v>1687</v>
@@ -12111,7 +12121,7 @@
         <v>1795</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="50">
         <v>35</v>
       </c>
@@ -12190,10 +12200,10 @@
         <v>Key-ABNT-35</v>
       </c>
       <c r="X35" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y35" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z35" s="54" t="s">
         <v>1688</v>
@@ -12202,7 +12212,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="50">
         <v>36</v>
       </c>
@@ -12281,10 +12291,10 @@
         <v>Key-ABNT-36</v>
       </c>
       <c r="X36" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y36" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z36" s="54" t="s">
         <v>1689</v>
@@ -12293,7 +12303,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="50">
         <v>37</v>
       </c>
@@ -12372,10 +12382,10 @@
         <v>Key-ABNT-37</v>
       </c>
       <c r="X37" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y37" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z37" s="54" t="s">
         <v>1690</v>
@@ -12384,7 +12394,7 @@
         <v>1798</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="50">
         <v>38</v>
       </c>
@@ -12463,10 +12473,10 @@
         <v>Key-ABNT-38</v>
       </c>
       <c r="X38" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y38" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z38" s="54" t="s">
         <v>1691</v>
@@ -12475,7 +12485,7 @@
         <v>1799</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="50">
         <v>39</v>
       </c>
@@ -12554,10 +12564,10 @@
         <v>Key-ABNT-39</v>
       </c>
       <c r="X39" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y39" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z39" s="54" t="s">
         <v>1692</v>
@@ -12566,7 +12576,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="50">
         <v>40</v>
       </c>
@@ -12645,10 +12655,10 @@
         <v>Key-ABNT-40</v>
       </c>
       <c r="X40" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y40" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z40" s="54" t="s">
         <v>1693</v>
@@ -12657,7 +12667,7 @@
         <v>1801</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="50">
         <v>41</v>
       </c>
@@ -12736,10 +12746,10 @@
         <v>Key-ABNT-41</v>
       </c>
       <c r="X41" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y41" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z41" s="54" t="s">
         <v>1694</v>
@@ -12748,7 +12758,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="50">
         <v>42</v>
       </c>
@@ -12827,10 +12837,10 @@
         <v>Key-ABNT-42</v>
       </c>
       <c r="X42" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y42" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z42" s="54" t="s">
         <v>1695</v>
@@ -12839,7 +12849,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="50">
         <v>43</v>
       </c>
@@ -12918,10 +12928,10 @@
         <v>Key-ABNT-43</v>
       </c>
       <c r="X43" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y43" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z43" s="54" t="s">
         <v>1696</v>
@@ -12930,7 +12940,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="50">
         <v>44</v>
       </c>
@@ -13009,10 +13019,10 @@
         <v>Key-ABNT-44</v>
       </c>
       <c r="X44" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y44" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z44" s="54" t="s">
         <v>1697</v>
@@ -13021,7 +13031,7 @@
         <v>1805</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="50">
         <v>45</v>
       </c>
@@ -13100,10 +13110,10 @@
         <v>Key-ABNT-45</v>
       </c>
       <c r="X45" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y45" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z45" s="54" t="s">
         <v>1698</v>
@@ -13112,7 +13122,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="50">
         <v>46</v>
       </c>
@@ -13191,10 +13201,10 @@
         <v>Key-ABNT-46</v>
       </c>
       <c r="X46" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y46" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z46" s="54" t="s">
         <v>1699</v>
@@ -13203,7 +13213,7 @@
         <v>1807</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="50">
         <v>47</v>
       </c>
@@ -13282,10 +13292,10 @@
         <v>Key-ABNT-47</v>
       </c>
       <c r="X47" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y47" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z47" s="54" t="s">
         <v>1700</v>
@@ -13294,7 +13304,7 @@
         <v>1808</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="50">
         <v>48</v>
       </c>
@@ -13373,10 +13383,10 @@
         <v>Key-ABNT-48</v>
       </c>
       <c r="X48" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y48" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z48" s="54" t="s">
         <v>1701</v>
@@ -13385,7 +13395,7 @@
         <v>1809</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="50">
         <v>49</v>
       </c>
@@ -13464,10 +13474,10 @@
         <v>Key-ABNT-49</v>
       </c>
       <c r="X49" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y49" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z49" s="54" t="s">
         <v>1702</v>
@@ -13476,7 +13486,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="50">
         <v>50</v>
       </c>
@@ -13555,10 +13565,10 @@
         <v>Key-ABNT-50</v>
       </c>
       <c r="X50" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y50" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z50" s="54" t="s">
         <v>1703</v>
@@ -13567,7 +13577,7 @@
         <v>1811</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="50">
         <v>51</v>
       </c>
@@ -13646,10 +13656,10 @@
         <v>Key-ABNT-51</v>
       </c>
       <c r="X51" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y51" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z51" s="54" t="s">
         <v>1704</v>
@@ -13658,7 +13668,7 @@
         <v>1812</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="50">
         <v>52</v>
       </c>
@@ -13737,10 +13747,10 @@
         <v>Key-ABNT-52</v>
       </c>
       <c r="X52" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y52" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z52" s="54" t="s">
         <v>1705</v>
@@ -13749,7 +13759,7 @@
         <v>1813</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="50">
         <v>53</v>
       </c>
@@ -13828,10 +13838,10 @@
         <v>Key-ABNT-53</v>
       </c>
       <c r="X53" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y53" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z53" s="54" t="s">
         <v>1706</v>
@@ -13840,7 +13850,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="50">
         <v>54</v>
       </c>
@@ -13919,10 +13929,10 @@
         <v>Key-ABNT-54</v>
       </c>
       <c r="X54" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y54" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z54" s="54" t="s">
         <v>1707</v>
@@ -13931,7 +13941,7 @@
         <v>1815</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="50">
         <v>55</v>
       </c>
@@ -14010,10 +14020,10 @@
         <v>Key-ABNT-55</v>
       </c>
       <c r="X55" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y55" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z55" s="54" t="s">
         <v>1708</v>
@@ -14022,7 +14032,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="50">
         <v>56</v>
       </c>
@@ -14101,10 +14111,10 @@
         <v>Key-ABNT-56</v>
       </c>
       <c r="X56" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y56" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z56" s="54" t="s">
         <v>1709</v>
@@ -14113,7 +14123,7 @@
         <v>1817</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="50">
         <v>57</v>
       </c>
@@ -14192,10 +14202,10 @@
         <v>Key-ABNT-57</v>
       </c>
       <c r="X57" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y57" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z57" s="54" t="s">
         <v>1710</v>
@@ -14204,7 +14214,7 @@
         <v>1818</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="50">
         <v>58</v>
       </c>
@@ -14283,10 +14293,10 @@
         <v>Key-ABNT-58</v>
       </c>
       <c r="X58" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y58" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z58" s="54" t="s">
         <v>1711</v>
@@ -14295,7 +14305,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="50">
         <v>59</v>
       </c>
@@ -14374,10 +14384,10 @@
         <v>Key-ABNT-59</v>
       </c>
       <c r="X59" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y59" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z59" s="54" t="s">
         <v>1712</v>
@@ -14386,7 +14396,7 @@
         <v>1820</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="50">
         <v>60</v>
       </c>
@@ -14465,10 +14475,10 @@
         <v>Key-ABNT-60</v>
       </c>
       <c r="X60" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y60" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z60" s="54" t="s">
         <v>1713</v>
@@ -14477,7 +14487,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="50">
         <v>61</v>
       </c>
@@ -14556,10 +14566,10 @@
         <v>Key-ABNT-61</v>
       </c>
       <c r="X61" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Y61" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="Z61" s="54" t="s">
         <v>1714</v>
@@ -14570,10 +14580,15 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:Y2">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA1:AA14 A2:B61">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14588,12 +14603,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7DB9369-35E2-4B4D-AD06-DBCD66EE066B}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
         <v>1472</v>
       </c>
@@ -14658,7 +14673,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="26">
         <v>2</v>
       </c>
@@ -14740,13 +14755,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5205260-7147-44D2-9997-02AF0D1204E5}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="16.33203125" customWidth="1"/>
+    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="16.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="29">
         <v>1</v>
       </c>
@@ -14757,7 +14772,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -14782,35 +14797,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79BA5E7-BFBD-4AC9-B36C-B9776AA17B75}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:Y722"/>
-  <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.296875" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.33203125" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.83203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="7.6640625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.296875" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.796875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="7.69921875" style="5" customWidth="1"/>
     <col min="6" max="6" width="5" style="44" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.6640625" style="44" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.69921875" style="44" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5" style="44" customWidth="1"/>
-    <col min="9" max="9" width="5.6640625" style="44" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.69921875" style="44" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5" style="44" customWidth="1"/>
-    <col min="11" max="11" width="16.6640625" style="44" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.69921875" style="44" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5" style="5" customWidth="1"/>
-    <col min="13" max="13" width="21.1640625" style="5" customWidth="1"/>
+    <col min="13" max="13" width="21.19921875" style="5" customWidth="1"/>
     <col min="14" max="14" width="7" style="44" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="52.1640625" style="44" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.33203125" style="5" customWidth="1"/>
-    <col min="17" max="17" width="5.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="52.19921875" style="44" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.296875" style="5" customWidth="1"/>
+    <col min="17" max="17" width="5.69921875" style="5" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" style="5" customWidth="1"/>
-    <col min="19" max="19" width="6.6640625" style="5" customWidth="1"/>
+    <col min="19" max="19" width="6.69921875" style="5" customWidth="1"/>
     <col min="20" max="20" width="6" style="5" customWidth="1"/>
-    <col min="21" max="21" width="6.6640625" style="5" customWidth="1"/>
+    <col min="21" max="21" width="6.69921875" style="5" customWidth="1"/>
     <col min="22" max="22" width="5" style="5" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="3.83203125" style="5" customWidth="1"/>
-    <col min="26" max="16384" width="11.33203125" style="5"/>
+    <col min="23" max="25" width="3.796875" style="5" customWidth="1"/>
+    <col min="26" max="16384" width="11.296875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>742</v>
       </c>
@@ -14883,7 +14898,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -14960,7 +14975,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -15037,7 +15052,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>4</v>
       </c>
@@ -15114,7 +15129,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>5</v>
       </c>
@@ -15191,7 +15206,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>6</v>
       </c>
@@ -15268,7 +15283,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>7</v>
       </c>
@@ -15345,7 +15360,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>8</v>
       </c>
@@ -15422,7 +15437,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>9</v>
       </c>
@@ -15499,7 +15514,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>10</v>
       </c>
@@ -15576,7 +15591,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>11</v>
       </c>
@@ -15653,7 +15668,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>12</v>
       </c>
@@ -15730,7 +15745,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>13</v>
       </c>
@@ -15807,7 +15822,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>14</v>
       </c>
@@ -15884,7 +15899,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>15</v>
       </c>
@@ -15961,7 +15976,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>16</v>
       </c>
@@ -16038,7 +16053,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>17</v>
       </c>
@@ -16115,7 +16130,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>18</v>
       </c>
@@ -16192,7 +16207,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>19</v>
       </c>
@@ -16269,7 +16284,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>20</v>
       </c>
@@ -16346,7 +16361,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>21</v>
       </c>
@@ -16423,7 +16438,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>22</v>
       </c>
@@ -16500,7 +16515,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>23</v>
       </c>
@@ -16577,7 +16592,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>24</v>
       </c>
@@ -16654,7 +16669,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>25</v>
       </c>
@@ -16731,7 +16746,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>26</v>
       </c>
@@ -16808,7 +16823,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>27</v>
       </c>
@@ -16885,7 +16900,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>28</v>
       </c>
@@ -16962,7 +16977,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>29</v>
       </c>
@@ -17039,7 +17054,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>30</v>
       </c>
@@ -17116,7 +17131,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>31</v>
       </c>
@@ -17193,7 +17208,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>32</v>
       </c>
@@ -17270,7 +17285,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>33</v>
       </c>
@@ -17347,7 +17362,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>34</v>
       </c>
@@ -17424,7 +17439,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>35</v>
       </c>
@@ -17501,7 +17516,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>36</v>
       </c>
@@ -17578,7 +17593,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>37</v>
       </c>
@@ -17655,7 +17670,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>38</v>
       </c>
@@ -17732,7 +17747,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>39</v>
       </c>
@@ -17809,7 +17824,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>40</v>
       </c>
@@ -17886,7 +17901,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>41</v>
       </c>
@@ -17963,7 +17978,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>42</v>
       </c>
@@ -18040,7 +18055,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>43</v>
       </c>
@@ -18117,7 +18132,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>44</v>
       </c>
@@ -18194,7 +18209,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>45</v>
       </c>
@@ -18271,7 +18286,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>46</v>
       </c>
@@ -18348,7 +18363,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>47</v>
       </c>
@@ -18425,7 +18440,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>48</v>
       </c>
@@ -18502,7 +18517,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>49</v>
       </c>
@@ -18579,7 +18594,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>50</v>
       </c>
@@ -18656,7 +18671,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>51</v>
       </c>
@@ -18733,7 +18748,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>52</v>
       </c>
@@ -18810,7 +18825,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>53</v>
       </c>
@@ -18887,7 +18902,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>54</v>
       </c>
@@ -18964,7 +18979,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>55</v>
       </c>
@@ -19041,7 +19056,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>56</v>
       </c>
@@ -19118,7 +19133,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>57</v>
       </c>
@@ -19195,7 +19210,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>58</v>
       </c>
@@ -19272,7 +19287,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>59</v>
       </c>
@@ -19349,7 +19364,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>60</v>
       </c>
@@ -19426,7 +19441,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>61</v>
       </c>
@@ -19503,7 +19518,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>62</v>
       </c>
@@ -19580,7 +19595,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>63</v>
       </c>
@@ -19657,7 +19672,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>64</v>
       </c>
@@ -19734,7 +19749,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>65</v>
       </c>
@@ -19811,7 +19826,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>66</v>
       </c>
@@ -19888,7 +19903,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>67</v>
       </c>
@@ -19965,7 +19980,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>68</v>
       </c>
@@ -20042,7 +20057,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>69</v>
       </c>
@@ -20119,7 +20134,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>70</v>
       </c>
@@ -20196,7 +20211,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>71</v>
       </c>
@@ -20273,7 +20288,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>72</v>
       </c>
@@ -20350,7 +20365,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>73</v>
       </c>
@@ -20427,7 +20442,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>74</v>
       </c>
@@ -20504,7 +20519,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>75</v>
       </c>
@@ -20581,7 +20596,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>76</v>
       </c>
@@ -20658,7 +20673,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>77</v>
       </c>
@@ -20735,7 +20750,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>78</v>
       </c>
@@ -20812,7 +20827,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>79</v>
       </c>
@@ -20889,7 +20904,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>80</v>
       </c>
@@ -20966,7 +20981,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>81</v>
       </c>
@@ -21043,7 +21058,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>82</v>
       </c>
@@ -21120,7 +21135,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>83</v>
       </c>
@@ -21197,7 +21212,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>84</v>
       </c>
@@ -21274,7 +21289,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
         <v>85</v>
       </c>
@@ -21351,7 +21366,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>86</v>
       </c>
@@ -21428,7 +21443,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>87</v>
       </c>
@@ -21505,7 +21520,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
         <v>88</v>
       </c>
@@ -21582,7 +21597,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>89</v>
       </c>
@@ -21659,7 +21674,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
         <v>90</v>
       </c>
@@ -21736,7 +21751,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>91</v>
       </c>
@@ -21813,7 +21828,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>92</v>
       </c>
@@ -21890,7 +21905,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
         <v>93</v>
       </c>
@@ -21967,7 +21982,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>94</v>
       </c>
@@ -22044,7 +22059,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>95</v>
       </c>
@@ -22121,7 +22136,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>96</v>
       </c>
@@ -22198,7 +22213,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>97</v>
       </c>
@@ -22275,7 +22290,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>98</v>
       </c>
@@ -22352,7 +22367,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
         <v>99</v>
       </c>
@@ -22429,7 +22444,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>100</v>
       </c>
@@ -22506,7 +22521,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>101</v>
       </c>
@@ -22583,7 +22598,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
         <v>102</v>
       </c>
@@ -22660,7 +22675,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
         <v>103</v>
       </c>
@@ -22737,7 +22752,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
         <v>104</v>
       </c>
@@ -22814,7 +22829,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
         <v>105</v>
       </c>
@@ -22891,7 +22906,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
         <v>106</v>
       </c>
@@ -22968,7 +22983,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
         <v>107</v>
       </c>
@@ -23045,7 +23060,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>108</v>
       </c>
@@ -23122,7 +23137,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
         <v>109</v>
       </c>
@@ -23199,7 +23214,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
         <v>110</v>
       </c>
@@ -23276,7 +23291,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
         <v>111</v>
       </c>
@@ -23353,7 +23368,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
         <v>112</v>
       </c>
@@ -23430,7 +23445,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
         <v>113</v>
       </c>
@@ -23507,7 +23522,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
         <v>114</v>
       </c>
@@ -23584,7 +23599,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
         <v>115</v>
       </c>
@@ -23661,7 +23676,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
         <v>116</v>
       </c>
@@ -23738,7 +23753,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
         <v>117</v>
       </c>
@@ -23815,7 +23830,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
         <v>118</v>
       </c>
@@ -23892,7 +23907,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
         <v>119</v>
       </c>
@@ -23969,7 +23984,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
         <v>120</v>
       </c>
@@ -24046,7 +24061,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
         <v>121</v>
       </c>
@@ -24123,7 +24138,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
         <v>122</v>
       </c>
@@ -24200,7 +24215,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
         <v>123</v>
       </c>
@@ -24277,7 +24292,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
         <v>124</v>
       </c>
@@ -24354,7 +24369,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
         <v>125</v>
       </c>
@@ -24431,7 +24446,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
         <v>126</v>
       </c>
@@ -24508,7 +24523,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
         <v>127</v>
       </c>
@@ -24585,7 +24600,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
         <v>128</v>
       </c>
@@ -24662,7 +24677,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
         <v>129</v>
       </c>
@@ -24739,7 +24754,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
         <v>130</v>
       </c>
@@ -24816,7 +24831,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
         <v>131</v>
       </c>
@@ -24893,7 +24908,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
         <v>132</v>
       </c>
@@ -24970,7 +24985,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6">
         <v>133</v>
       </c>
@@ -25047,7 +25062,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="6">
         <v>134</v>
       </c>
@@ -25124,7 +25139,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="6">
         <v>135</v>
       </c>
@@ -25201,7 +25216,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="6">
         <v>136</v>
       </c>
@@ -25278,7 +25293,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="6">
         <v>137</v>
       </c>
@@ -25355,7 +25370,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
         <v>138</v>
       </c>
@@ -25432,7 +25447,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="6">
         <v>139</v>
       </c>
@@ -25509,7 +25524,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
         <v>140</v>
       </c>
@@ -25586,7 +25601,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="6">
         <v>141</v>
       </c>
@@ -25663,7 +25678,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
         <v>142</v>
       </c>
@@ -25740,7 +25755,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="6">
         <v>143</v>
       </c>
@@ -25817,7 +25832,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
         <v>144</v>
       </c>
@@ -25894,7 +25909,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="6">
         <v>145</v>
       </c>
@@ -25971,7 +25986,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
         <v>146</v>
       </c>
@@ -26048,7 +26063,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
         <v>147</v>
       </c>
@@ -26125,7 +26140,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
         <v>148</v>
       </c>
@@ -26202,7 +26217,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="149" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="6">
         <v>149</v>
       </c>
@@ -26279,7 +26294,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6">
         <v>150</v>
       </c>
@@ -26356,7 +26371,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
         <v>151</v>
       </c>
@@ -26433,7 +26448,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="6">
         <v>152</v>
       </c>
@@ -26510,7 +26525,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="6">
         <v>153</v>
       </c>
@@ -26587,7 +26602,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="6">
         <v>154</v>
       </c>
@@ -26664,7 +26679,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="6">
         <v>155</v>
       </c>
@@ -26741,7 +26756,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="156" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="6">
         <v>156</v>
       </c>
@@ -26818,7 +26833,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="6">
         <v>157</v>
       </c>
@@ -26895,7 +26910,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="158" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="6">
         <v>158</v>
       </c>
@@ -26972,7 +26987,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="159" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="6">
         <v>159</v>
       </c>
@@ -27049,7 +27064,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="160" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="6">
         <v>160</v>
       </c>
@@ -27126,7 +27141,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="161" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="6">
         <v>161</v>
       </c>
@@ -27203,7 +27218,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="162" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="6">
         <v>162</v>
       </c>
@@ -27280,7 +27295,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="163" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="6">
         <v>163</v>
       </c>
@@ -27357,7 +27372,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="164" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="6">
         <v>164</v>
       </c>
@@ -27434,7 +27449,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="165" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="6">
         <v>165</v>
       </c>
@@ -27511,7 +27526,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="166" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="6">
         <v>166</v>
       </c>
@@ -27588,7 +27603,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="167" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="6">
         <v>167</v>
       </c>
@@ -27665,7 +27680,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="168" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6">
         <v>168</v>
       </c>
@@ -27742,7 +27757,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="169" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="6">
         <v>169</v>
       </c>
@@ -27819,7 +27834,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="170" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="6">
         <v>170</v>
       </c>
@@ -27896,7 +27911,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="171" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="6">
         <v>171</v>
       </c>
@@ -27973,7 +27988,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="172" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="6">
         <v>172</v>
       </c>
@@ -28050,7 +28065,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="173" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="6">
         <v>173</v>
       </c>
@@ -28127,7 +28142,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="174" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="6">
         <v>174</v>
       </c>
@@ -28204,7 +28219,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="175" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="6">
         <v>175</v>
       </c>
@@ -28281,7 +28296,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="176" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="6">
         <v>176</v>
       </c>
@@ -28358,7 +28373,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="177" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="6">
         <v>177</v>
       </c>
@@ -28435,7 +28450,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="178" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="6">
         <v>178</v>
       </c>
@@ -28512,7 +28527,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="179" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="6">
         <v>179</v>
       </c>
@@ -28589,7 +28604,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="180" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="6">
         <v>180</v>
       </c>
@@ -28666,7 +28681,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="181" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="6">
         <v>181</v>
       </c>
@@ -28743,7 +28758,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="182" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="6">
         <v>182</v>
       </c>
@@ -28820,7 +28835,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="183" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="6">
         <v>183</v>
       </c>
@@ -28897,7 +28912,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="184" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="6">
         <v>184</v>
       </c>
@@ -28974,7 +28989,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="185" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6">
         <v>185</v>
       </c>
@@ -29051,7 +29066,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="186" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="6">
         <v>186</v>
       </c>
@@ -29128,7 +29143,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="187" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="6">
         <v>187</v>
       </c>
@@ -29205,7 +29220,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="188" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="6">
         <v>188</v>
       </c>
@@ -29282,7 +29297,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="189" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="6">
         <v>189</v>
       </c>
@@ -29359,7 +29374,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="190" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="6">
         <v>190</v>
       </c>
@@ -29436,7 +29451,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="191" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="6">
         <v>191</v>
       </c>
@@ -29513,7 +29528,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="192" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="6">
         <v>192</v>
       </c>
@@ -29590,7 +29605,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="193" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="6">
         <v>193</v>
       </c>
@@ -29667,7 +29682,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="194" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="6">
         <v>194</v>
       </c>
@@ -29744,7 +29759,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="195" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="6">
         <v>195</v>
       </c>
@@ -29821,7 +29836,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="196" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="6">
         <v>196</v>
       </c>
@@ -29898,7 +29913,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="197" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="6">
         <v>197</v>
       </c>
@@ -29975,7 +29990,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="198" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="6">
         <v>198</v>
       </c>
@@ -30052,7 +30067,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="199" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="6">
         <v>199</v>
       </c>
@@ -30129,7 +30144,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="200" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="6">
         <v>200</v>
       </c>
@@ -30206,7 +30221,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="201" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6">
         <v>201</v>
       </c>
@@ -30283,7 +30298,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="202" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="6">
         <v>202</v>
       </c>
@@ -30360,7 +30375,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="203" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="6">
         <v>203</v>
       </c>
@@ -30437,7 +30452,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="204" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="6">
         <v>204</v>
       </c>
@@ -30514,7 +30529,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="205" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="6">
         <v>205</v>
       </c>
@@ -30591,7 +30606,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="206" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="6">
         <v>206</v>
       </c>
@@ -30668,7 +30683,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="207" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="6">
         <v>207</v>
       </c>
@@ -30745,7 +30760,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="208" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="6">
         <v>208</v>
       </c>
@@ -30822,7 +30837,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="209" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="6">
         <v>209</v>
       </c>
@@ -30899,7 +30914,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="210" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="6">
         <v>210</v>
       </c>
@@ -30976,7 +30991,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="211" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="6">
         <v>211</v>
       </c>
@@ -31053,7 +31068,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="212" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="6">
         <v>212</v>
       </c>
@@ -31130,7 +31145,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="213" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="6">
         <v>213</v>
       </c>
@@ -31207,7 +31222,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="214" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="6">
         <v>214</v>
       </c>
@@ -31284,7 +31299,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="215" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="6">
         <v>215</v>
       </c>
@@ -31361,7 +31376,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="216" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="6">
         <v>216</v>
       </c>
@@ -31438,7 +31453,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="217" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="6">
         <v>217</v>
       </c>
@@ -31515,7 +31530,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="218" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="6">
         <v>218</v>
       </c>
@@ -31592,7 +31607,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="219" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="6">
         <v>219</v>
       </c>
@@ -31669,7 +31684,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="220" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6">
         <v>220</v>
       </c>
@@ -31746,7 +31761,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="221" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="6">
         <v>221</v>
       </c>
@@ -31823,7 +31838,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="222" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="6">
         <v>222</v>
       </c>
@@ -31900,7 +31915,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="223" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="6">
         <v>223</v>
       </c>
@@ -31977,7 +31992,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="224" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="6">
         <v>224</v>
       </c>
@@ -32054,7 +32069,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="225" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="6">
         <v>225</v>
       </c>
@@ -32131,7 +32146,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="226" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="6">
         <v>226</v>
       </c>
@@ -32208,7 +32223,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="227" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="6">
         <v>227</v>
       </c>
@@ -32285,7 +32300,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="228" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="6">
         <v>228</v>
       </c>
@@ -32362,7 +32377,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="229" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="6">
         <v>229</v>
       </c>
@@ -32439,7 +32454,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="230" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="6">
         <v>230</v>
       </c>
@@ -32516,7 +32531,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="231" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="6">
         <v>231</v>
       </c>
@@ -32593,7 +32608,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="232" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="6">
         <v>232</v>
       </c>
@@ -32670,7 +32685,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="233" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="6">
         <v>233</v>
       </c>
@@ -32747,7 +32762,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="234" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="6">
         <v>234</v>
       </c>
@@ -32824,7 +32839,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="235" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="6">
         <v>235</v>
       </c>
@@ -32901,7 +32916,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="236" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="6">
         <v>236</v>
       </c>
@@ -32978,7 +32993,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="237" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6">
         <v>237</v>
       </c>
@@ -33055,7 +33070,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="238" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="6">
         <v>238</v>
       </c>
@@ -33132,7 +33147,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="239" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="6">
         <v>239</v>
       </c>
@@ -33209,7 +33224,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="240" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="6">
         <v>240</v>
       </c>
@@ -33286,7 +33301,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="241" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="6">
         <v>241</v>
       </c>
@@ -33363,7 +33378,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="242" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="6">
         <v>242</v>
       </c>
@@ -33440,7 +33455,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="243" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="6">
         <v>243</v>
       </c>
@@ -33517,7 +33532,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="244" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="6">
         <v>244</v>
       </c>
@@ -33594,7 +33609,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="245" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="6">
         <v>245</v>
       </c>
@@ -33671,7 +33686,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="246" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="6">
         <v>246</v>
       </c>
@@ -33748,7 +33763,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="247" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="6">
         <v>247</v>
       </c>
@@ -33825,7 +33840,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="248" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="6">
         <v>248</v>
       </c>
@@ -33902,7 +33917,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="249" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="6">
         <v>249</v>
       </c>
@@ -33979,7 +33994,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="250" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="6">
         <v>250</v>
       </c>
@@ -34056,7 +34071,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="251" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="6">
         <v>251</v>
       </c>
@@ -34133,7 +34148,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="252" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="6">
         <v>252</v>
       </c>
@@ -34210,7 +34225,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="253" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="6">
         <v>253</v>
       </c>
@@ -34287,7 +34302,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="254" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="6">
         <v>254</v>
       </c>
@@ -34364,7 +34379,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="255" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6">
         <v>255</v>
       </c>
@@ -34441,7 +34456,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="256" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="6">
         <v>256</v>
       </c>
@@ -34518,7 +34533,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="257" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="6">
         <v>257</v>
       </c>
@@ -34595,7 +34610,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="258" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="6">
         <v>258</v>
       </c>
@@ -34672,7 +34687,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="259" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="6">
         <v>259</v>
       </c>
@@ -34749,7 +34764,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="260" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="6">
         <v>260</v>
       </c>
@@ -34826,7 +34841,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="261" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="6">
         <v>261</v>
       </c>
@@ -34903,7 +34918,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="262" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="6">
         <v>262</v>
       </c>
@@ -34980,7 +34995,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="263" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="6">
         <v>263</v>
       </c>
@@ -35057,7 +35072,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="264" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="6">
         <v>264</v>
       </c>
@@ -35134,7 +35149,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="265" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="6">
         <v>265</v>
       </c>
@@ -35211,7 +35226,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="266" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="6">
         <v>266</v>
       </c>
@@ -35288,7 +35303,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="267" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="6">
         <v>267</v>
       </c>
@@ -35365,7 +35380,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="268" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="6">
         <v>268</v>
       </c>
@@ -35442,7 +35457,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="269" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="6">
         <v>269</v>
       </c>
@@ -35519,7 +35534,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="270" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="6">
         <v>270</v>
       </c>
@@ -35596,7 +35611,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="271" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="6">
         <v>271</v>
       </c>
@@ -35673,7 +35688,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="272" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="6">
         <v>272</v>
       </c>
@@ -35750,7 +35765,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="273" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="6">
         <v>273</v>
       </c>
@@ -35827,7 +35842,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="274" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6">
         <v>274</v>
       </c>
@@ -35904,7 +35919,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="275" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="6">
         <v>275</v>
       </c>
@@ -35981,7 +35996,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="276" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="6">
         <v>276</v>
       </c>
@@ -36058,7 +36073,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="277" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="6">
         <v>277</v>
       </c>
@@ -36135,7 +36150,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="278" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="6">
         <v>278</v>
       </c>
@@ -36212,7 +36227,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="279" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="6">
         <v>279</v>
       </c>
@@ -36289,7 +36304,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="280" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="6">
         <v>280</v>
       </c>
@@ -36366,7 +36381,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="281" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="6">
         <v>281</v>
       </c>
@@ -36443,7 +36458,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="282" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="6">
         <v>282</v>
       </c>
@@ -36520,7 +36535,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="283" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="6">
         <v>283</v>
       </c>
@@ -36597,7 +36612,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="284" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="6">
         <v>284</v>
       </c>
@@ -36674,7 +36689,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="285" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="6">
         <v>285</v>
       </c>
@@ -36751,7 +36766,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="286" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="6">
         <v>286</v>
       </c>
@@ -36828,7 +36843,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="287" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="6">
         <v>287</v>
       </c>
@@ -36905,7 +36920,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="288" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="6">
         <v>288</v>
       </c>
@@ -36982,7 +36997,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="289" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="6">
         <v>289</v>
       </c>
@@ -37059,7 +37074,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="290" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="6">
         <v>290</v>
       </c>
@@ -37136,7 +37151,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="291" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="6">
         <v>291</v>
       </c>
@@ -37213,7 +37228,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="292" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="6">
         <v>292</v>
       </c>
@@ -37290,7 +37305,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="293" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6">
         <v>293</v>
       </c>
@@ -37367,7 +37382,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="294" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="6">
         <v>294</v>
       </c>
@@ -37444,7 +37459,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="295" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="6">
         <v>295</v>
       </c>
@@ -37521,7 +37536,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="296" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="6">
         <v>296</v>
       </c>
@@ -37598,7 +37613,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="297" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="6">
         <v>297</v>
       </c>
@@ -37675,7 +37690,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="298" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="6">
         <v>298</v>
       </c>
@@ -37752,7 +37767,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="299" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="6">
         <v>299</v>
       </c>
@@ -37829,7 +37844,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="300" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="6">
         <v>300</v>
       </c>
@@ -37906,7 +37921,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="301" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="6">
         <v>301</v>
       </c>
@@ -37983,7 +37998,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="302" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="6">
         <v>302</v>
       </c>
@@ -38060,7 +38075,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="303" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="6">
         <v>303</v>
       </c>
@@ -38137,7 +38152,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="304" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="6">
         <v>304</v>
       </c>
@@ -38214,7 +38229,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="305" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="6">
         <v>305</v>
       </c>
@@ -38291,7 +38306,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="306" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="6">
         <v>306</v>
       </c>
@@ -38368,7 +38383,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="307" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="6">
         <v>307</v>
       </c>
@@ -38445,7 +38460,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="308" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="6">
         <v>308</v>
       </c>
@@ -38522,7 +38537,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="309" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="6">
         <v>309</v>
       </c>
@@ -38599,7 +38614,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="310" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="6">
         <v>310</v>
       </c>
@@ -38676,7 +38691,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="311" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="6">
         <v>311</v>
       </c>
@@ -38753,7 +38768,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="312" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6">
         <v>312</v>
       </c>
@@ -38830,7 +38845,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="313" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="6">
         <v>313</v>
       </c>
@@ -38907,7 +38922,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="314" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="6">
         <v>314</v>
       </c>
@@ -38984,7 +38999,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="315" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="6">
         <v>315</v>
       </c>
@@ -39061,7 +39076,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="316" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="6">
         <v>316</v>
       </c>
@@ -39138,7 +39153,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="317" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="6">
         <v>317</v>
       </c>
@@ -39215,7 +39230,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="318" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="6">
         <v>318</v>
       </c>
@@ -39292,7 +39307,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="319" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="6">
         <v>319</v>
       </c>
@@ -39369,7 +39384,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="320" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="6">
         <v>320</v>
       </c>
@@ -39446,7 +39461,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="321" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="6">
         <v>321</v>
       </c>
@@ -39523,7 +39538,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="322" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="6">
         <v>322</v>
       </c>
@@ -39600,7 +39615,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="323" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="6">
         <v>323</v>
       </c>
@@ -39677,7 +39692,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="324" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="6">
         <v>324</v>
       </c>
@@ -39754,7 +39769,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="325" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="6">
         <v>325</v>
       </c>
@@ -39831,7 +39846,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="326" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="6">
         <v>326</v>
       </c>
@@ -39908,7 +39923,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="327" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="6">
         <v>327</v>
       </c>
@@ -39985,7 +40000,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="328" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="6">
         <v>328</v>
       </c>
@@ -40062,7 +40077,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="329" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="6">
         <v>329</v>
       </c>
@@ -40139,7 +40154,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="330" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="6">
         <v>330</v>
       </c>
@@ -40216,7 +40231,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="331" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="6">
         <v>331</v>
       </c>
@@ -40293,7 +40308,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="332" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="6">
         <v>332</v>
       </c>
@@ -40370,7 +40385,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="333" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="6">
         <v>333</v>
       </c>
@@ -40447,7 +40462,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="334" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="6">
         <v>334</v>
       </c>
@@ -40524,7 +40539,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="335" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="6">
         <v>335</v>
       </c>
@@ -40601,7 +40616,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="336" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="6">
         <v>336</v>
       </c>
@@ -40678,7 +40693,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="337" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="6">
         <v>337</v>
       </c>
@@ -40755,7 +40770,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="338" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="6">
         <v>338</v>
       </c>
@@ -40832,7 +40847,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="339" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="6">
         <v>339</v>
       </c>
@@ -40909,7 +40924,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="340" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="6">
         <v>340</v>
       </c>
@@ -40986,7 +41001,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="341" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="6">
         <v>341</v>
       </c>
@@ -41063,7 +41078,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="342" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="6">
         <v>342</v>
       </c>
@@ -41140,7 +41155,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="343" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="6">
         <v>343</v>
       </c>
@@ -41217,7 +41232,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="344" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="6">
         <v>344</v>
       </c>
@@ -41294,7 +41309,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="345" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="6">
         <v>345</v>
       </c>
@@ -41371,7 +41386,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="346" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="6">
         <v>346</v>
       </c>
@@ -41448,7 +41463,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="347" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="6">
         <v>347</v>
       </c>
@@ -41525,7 +41540,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="348" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="6">
         <v>348</v>
       </c>
@@ -41602,7 +41617,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="349" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="6">
         <v>349</v>
       </c>
@@ -41679,7 +41694,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="350" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="6">
         <v>350</v>
       </c>
@@ -41756,7 +41771,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="351" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="6">
         <v>351</v>
       </c>
@@ -41833,7 +41848,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="352" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="6">
         <v>352</v>
       </c>
@@ -41910,7 +41925,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="353" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="6">
         <v>353</v>
       </c>
@@ -41987,7 +42002,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="354" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="6">
         <v>354</v>
       </c>
@@ -42064,7 +42079,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="355" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="6">
         <v>355</v>
       </c>
@@ -42141,7 +42156,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="356" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="6">
         <v>356</v>
       </c>
@@ -42218,7 +42233,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="357" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="6">
         <v>357</v>
       </c>
@@ -42295,7 +42310,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="358" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="6">
         <v>358</v>
       </c>
@@ -42372,7 +42387,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="359" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="6">
         <v>359</v>
       </c>
@@ -42449,7 +42464,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="360" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="6">
         <v>360</v>
       </c>
@@ -42526,7 +42541,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="361" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="6">
         <v>361</v>
       </c>
@@ -42603,7 +42618,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="362" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="6">
         <v>362</v>
       </c>
@@ -42680,7 +42695,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="363" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="6">
         <v>363</v>
       </c>
@@ -42757,7 +42772,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="364" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="6">
         <v>364</v>
       </c>
@@ -42834,7 +42849,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="365" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="6">
         <v>365</v>
       </c>
@@ -42911,7 +42926,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="366" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="6">
         <v>366</v>
       </c>
@@ -42988,7 +43003,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="367" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="6">
         <v>367</v>
       </c>
@@ -43065,7 +43080,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="368" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="6">
         <v>368</v>
       </c>
@@ -43142,7 +43157,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="369" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="6">
         <v>369</v>
       </c>
@@ -43219,7 +43234,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="370" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="6">
         <v>370</v>
       </c>
@@ -43296,7 +43311,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="371" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="6">
         <v>371</v>
       </c>
@@ -43373,7 +43388,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="372" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="6">
         <v>372</v>
       </c>
@@ -43450,7 +43465,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="373" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="6">
         <v>373</v>
       </c>
@@ -43527,7 +43542,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="374" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="6">
         <v>374</v>
       </c>
@@ -43604,7 +43619,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="375" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="6">
         <v>375</v>
       </c>
@@ -43681,7 +43696,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="376" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="6">
         <v>376</v>
       </c>
@@ -43758,7 +43773,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="377" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="6">
         <v>377</v>
       </c>
@@ -43835,7 +43850,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="378" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="6">
         <v>378</v>
       </c>
@@ -43912,7 +43927,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="379" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="6">
         <v>379</v>
       </c>
@@ -43989,7 +44004,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="380" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="6">
         <v>380</v>
       </c>
@@ -44066,7 +44081,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="381" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="6">
         <v>381</v>
       </c>
@@ -44143,7 +44158,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="382" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="6">
         <v>382</v>
       </c>
@@ -44220,7 +44235,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="383" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="6">
         <v>383</v>
       </c>
@@ -44297,7 +44312,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="384" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="6">
         <v>384</v>
       </c>
@@ -44374,7 +44389,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="385" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="6">
         <v>385</v>
       </c>
@@ -44451,7 +44466,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="386" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="6">
         <v>386</v>
       </c>
@@ -44528,7 +44543,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="387" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="6">
         <v>387</v>
       </c>
@@ -44605,7 +44620,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="388" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="6">
         <v>388</v>
       </c>
@@ -44682,7 +44697,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="389" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="6">
         <v>389</v>
       </c>
@@ -44759,7 +44774,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="390" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="6">
         <v>390</v>
       </c>
@@ -44836,7 +44851,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="391" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="6">
         <v>391</v>
       </c>
@@ -44913,7 +44928,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="392" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="6">
         <v>392</v>
       </c>
@@ -44990,7 +45005,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="393" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="6">
         <v>393</v>
       </c>
@@ -45067,7 +45082,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="394" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="6">
         <v>394</v>
       </c>
@@ -45144,7 +45159,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="395" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="6">
         <v>395</v>
       </c>
@@ -45221,7 +45236,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="396" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="6">
         <v>396</v>
       </c>
@@ -45298,7 +45313,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="397" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="6">
         <v>397</v>
       </c>
@@ -45375,7 +45390,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="398" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="6">
         <v>398</v>
       </c>
@@ -45452,7 +45467,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="399" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="6">
         <v>399</v>
       </c>
@@ -45529,7 +45544,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="400" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="6">
         <v>400</v>
       </c>
@@ -45606,7 +45621,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="401" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="6">
         <v>401</v>
       </c>
@@ -45683,7 +45698,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="402" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="6">
         <v>402</v>
       </c>
@@ -45760,7 +45775,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="403" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="6">
         <v>403</v>
       </c>
@@ -45837,7 +45852,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="404" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="6">
         <v>404</v>
       </c>
@@ -45914,7 +45929,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="405" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="6">
         <v>405</v>
       </c>
@@ -45991,7 +46006,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="406" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="6">
         <v>406</v>
       </c>
@@ -46068,7 +46083,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="407" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="6">
         <v>407</v>
       </c>
@@ -46145,7 +46160,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="408" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="6">
         <v>408</v>
       </c>
@@ -46222,7 +46237,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="409" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="6">
         <v>409</v>
       </c>
@@ -46299,7 +46314,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="410" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="6">
         <v>410</v>
       </c>
@@ -46376,7 +46391,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="411" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="6">
         <v>411</v>
       </c>
@@ -46453,7 +46468,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="412" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="6">
         <v>412</v>
       </c>
@@ -46530,7 +46545,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="413" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="6">
         <v>413</v>
       </c>
@@ -46607,7 +46622,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="414" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="6">
         <v>414</v>
       </c>
@@ -46684,7 +46699,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="415" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="6">
         <v>415</v>
       </c>
@@ -46761,7 +46776,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="416" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="6">
         <v>416</v>
       </c>
@@ -46838,7 +46853,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="417" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="6">
         <v>417</v>
       </c>
@@ -46915,7 +46930,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="418" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="6">
         <v>418</v>
       </c>
@@ -46992,7 +47007,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="419" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="6">
         <v>419</v>
       </c>
@@ -47069,7 +47084,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="420" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="6">
         <v>420</v>
       </c>
@@ -47146,7 +47161,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="421" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="6">
         <v>421</v>
       </c>
@@ -47223,7 +47238,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="422" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="6">
         <v>422</v>
       </c>
@@ -47300,7 +47315,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="423" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="6">
         <v>423</v>
       </c>
@@ -47377,7 +47392,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="424" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="6">
         <v>424</v>
       </c>
@@ -47454,7 +47469,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="425" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="6">
         <v>425</v>
       </c>
@@ -47531,7 +47546,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="426" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="6">
         <v>426</v>
       </c>
@@ -47608,7 +47623,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="427" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="6">
         <v>427</v>
       </c>
@@ -47685,7 +47700,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="428" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="6">
         <v>428</v>
       </c>
@@ -47762,7 +47777,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="429" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="6">
         <v>429</v>
       </c>
@@ -47839,7 +47854,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="430" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="6">
         <v>430</v>
       </c>
@@ -47916,7 +47931,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="431" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="6">
         <v>431</v>
       </c>
@@ -47993,7 +48008,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="432" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="6">
         <v>432</v>
       </c>
@@ -48070,7 +48085,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="433" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="6">
         <v>433</v>
       </c>
@@ -48147,7 +48162,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="434" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="6">
         <v>434</v>
       </c>
@@ -48224,7 +48239,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="435" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="6">
         <v>435</v>
       </c>
@@ -48301,7 +48316,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="436" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="6">
         <v>436</v>
       </c>
@@ -48378,7 +48393,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="437" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="6">
         <v>437</v>
       </c>
@@ -48455,7 +48470,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="438" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="6">
         <v>438</v>
       </c>
@@ -48532,7 +48547,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="439" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="6">
         <v>439</v>
       </c>
@@ -48609,7 +48624,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="440" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="6">
         <v>440</v>
       </c>
@@ -48686,7 +48701,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="441" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="6">
         <v>441</v>
       </c>
@@ -48763,7 +48778,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="442" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="6">
         <v>442</v>
       </c>
@@ -48840,7 +48855,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="443" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="6">
         <v>443</v>
       </c>
@@ -48917,7 +48932,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="444" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="6">
         <v>444</v>
       </c>
@@ -48994,7 +49009,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="445" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="6">
         <v>445</v>
       </c>
@@ -49071,7 +49086,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="446" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="6">
         <v>446</v>
       </c>
@@ -49148,7 +49163,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="447" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="6">
         <v>447</v>
       </c>
@@ -49225,7 +49240,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="448" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="6">
         <v>448</v>
       </c>
@@ -49302,7 +49317,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="449" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="6">
         <v>449</v>
       </c>
@@ -49379,7 +49394,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="450" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="6">
         <v>450</v>
       </c>
@@ -49456,7 +49471,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="451" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="6">
         <v>451</v>
       </c>
@@ -49533,7 +49548,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="452" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="6">
         <v>452</v>
       </c>
@@ -49610,7 +49625,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="453" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="6">
         <v>453</v>
       </c>
@@ -49687,7 +49702,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="454" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="6">
         <v>454</v>
       </c>
@@ -49764,7 +49779,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="455" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="6">
         <v>455</v>
       </c>
@@ -49841,7 +49856,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="456" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="6">
         <v>456</v>
       </c>
@@ -49918,7 +49933,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="457" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="6">
         <v>457</v>
       </c>
@@ -49995,7 +50010,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="458" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="6">
         <v>458</v>
       </c>
@@ -50072,7 +50087,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="459" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="6">
         <v>459</v>
       </c>
@@ -50149,7 +50164,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="460" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="6">
         <v>460</v>
       </c>
@@ -50226,7 +50241,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="461" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="6">
         <v>461</v>
       </c>
@@ -50303,7 +50318,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="462" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="6">
         <v>462</v>
       </c>
@@ -50380,7 +50395,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="463" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="6">
         <v>463</v>
       </c>
@@ -50457,7 +50472,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="464" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="6">
         <v>464</v>
       </c>
@@ -50534,7 +50549,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="465" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="6">
         <v>465</v>
       </c>
@@ -50611,7 +50626,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="466" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="6">
         <v>466</v>
       </c>
@@ -50688,7 +50703,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="467" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="6">
         <v>467</v>
       </c>
@@ -50765,7 +50780,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="468" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="6">
         <v>468</v>
       </c>
@@ -50842,7 +50857,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="469" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="6">
         <v>469</v>
       </c>
@@ -50919,7 +50934,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="470" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="6">
         <v>470</v>
       </c>
@@ -50996,7 +51011,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="471" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="6">
         <v>471</v>
       </c>
@@ -51073,7 +51088,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="472" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="6">
         <v>472</v>
       </c>
@@ -51150,7 +51165,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="473" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="6">
         <v>473</v>
       </c>
@@ -51227,7 +51242,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="474" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="6">
         <v>474</v>
       </c>
@@ -51304,7 +51319,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="475" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="6">
         <v>475</v>
       </c>
@@ -51381,7 +51396,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="476" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="6">
         <v>476</v>
       </c>
@@ -51458,7 +51473,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="477" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="6">
         <v>477</v>
       </c>
@@ -51535,7 +51550,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="478" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="6">
         <v>478</v>
       </c>
@@ -51612,7 +51627,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="479" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="6">
         <v>479</v>
       </c>
@@ -51689,7 +51704,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="480" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="6">
         <v>480</v>
       </c>
@@ -51766,7 +51781,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="481" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="6">
         <v>481</v>
       </c>
@@ -51843,7 +51858,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="482" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="6">
         <v>482</v>
       </c>
@@ -51920,7 +51935,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="483" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="6">
         <v>483</v>
       </c>
@@ -51997,7 +52012,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="484" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="6">
         <v>484</v>
       </c>
@@ -52074,7 +52089,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="485" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="6">
         <v>485</v>
       </c>
@@ -52151,7 +52166,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="486" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="6">
         <v>486</v>
       </c>
@@ -52228,7 +52243,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="487" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="6">
         <v>487</v>
       </c>
@@ -52305,7 +52320,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="488" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="6">
         <v>488</v>
       </c>
@@ -52382,7 +52397,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="489" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="6">
         <v>489</v>
       </c>
@@ -52459,7 +52474,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="490" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="6">
         <v>490</v>
       </c>
@@ -52536,7 +52551,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="491" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="6">
         <v>491</v>
       </c>
@@ -52613,7 +52628,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="492" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="6">
         <v>492</v>
       </c>
@@ -52690,7 +52705,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="493" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="6">
         <v>493</v>
       </c>
@@ -52767,7 +52782,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="494" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="6">
         <v>494</v>
       </c>
@@ -52844,7 +52859,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="495" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="6">
         <v>495</v>
       </c>
@@ -52921,7 +52936,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="496" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="6">
         <v>496</v>
       </c>
@@ -52998,7 +53013,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="497" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="6">
         <v>497</v>
       </c>
@@ -53075,7 +53090,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="498" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="6">
         <v>498</v>
       </c>
@@ -53152,7 +53167,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="499" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="6">
         <v>499</v>
       </c>
@@ -53229,7 +53244,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="500" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="6">
         <v>500</v>
       </c>
@@ -53306,7 +53321,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="501" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="6">
         <v>501</v>
       </c>
@@ -53383,7 +53398,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="502" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="6">
         <v>502</v>
       </c>
@@ -53460,7 +53475,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="503" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="6">
         <v>503</v>
       </c>
@@ -53537,7 +53552,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="504" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="6">
         <v>504</v>
       </c>
@@ -53614,7 +53629,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="505" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="6">
         <v>505</v>
       </c>
@@ -53691,7 +53706,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="506" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="6">
         <v>506</v>
       </c>
@@ -53768,7 +53783,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="507" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="6">
         <v>507</v>
       </c>
@@ -53845,7 +53860,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="508" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="6">
         <v>508</v>
       </c>
@@ -53922,7 +53937,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="509" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="6">
         <v>509</v>
       </c>
@@ -53999,7 +54014,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="510" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="6">
         <v>510</v>
       </c>
@@ -54076,7 +54091,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="511" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="6">
         <v>511</v>
       </c>
@@ -54153,7 +54168,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="512" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="6">
         <v>512</v>
       </c>
@@ -54230,7 +54245,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="513" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="6">
         <v>513</v>
       </c>
@@ -54307,7 +54322,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="514" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="6">
         <v>514</v>
       </c>
@@ -54384,7 +54399,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="515" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="6">
         <v>515</v>
       </c>
@@ -54461,7 +54476,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="516" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="6">
         <v>516</v>
       </c>
@@ -54538,7 +54553,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="517" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="6">
         <v>517</v>
       </c>
@@ -54615,7 +54630,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="518" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="6">
         <v>518</v>
       </c>
@@ -54692,7 +54707,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="519" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="6">
         <v>519</v>
       </c>
@@ -54769,7 +54784,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="520" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="6">
         <v>520</v>
       </c>
@@ -54846,7 +54861,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="521" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="6">
         <v>521</v>
       </c>
@@ -54923,7 +54938,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="522" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="6">
         <v>522</v>
       </c>
@@ -55000,7 +55015,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="523" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="6">
         <v>523</v>
       </c>
@@ -55077,7 +55092,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="524" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="6">
         <v>524</v>
       </c>
@@ -55154,7 +55169,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="525" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="6">
         <v>525</v>
       </c>
@@ -55231,7 +55246,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="526" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="6">
         <v>526</v>
       </c>
@@ -55308,7 +55323,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="527" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="6">
         <v>527</v>
       </c>
@@ -55385,7 +55400,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="528" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="6">
         <v>528</v>
       </c>
@@ -55462,7 +55477,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="529" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="6">
         <v>529</v>
       </c>
@@ -55539,7 +55554,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="530" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="6">
         <v>530</v>
       </c>
@@ -55616,7 +55631,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="531" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="6">
         <v>531</v>
       </c>
@@ -55693,7 +55708,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="532" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="6">
         <v>532</v>
       </c>
@@ -55770,7 +55785,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="533" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="6">
         <v>533</v>
       </c>
@@ -55847,7 +55862,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="534" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="6">
         <v>534</v>
       </c>
@@ -55924,7 +55939,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="535" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="6">
         <v>535</v>
       </c>
@@ -56001,7 +56016,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="536" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="6">
         <v>536</v>
       </c>
@@ -56078,7 +56093,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="537" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="6">
         <v>537</v>
       </c>
@@ -56155,7 +56170,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="538" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="6">
         <v>538</v>
       </c>
@@ -56232,7 +56247,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="539" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="6">
         <v>539</v>
       </c>
@@ -56309,7 +56324,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="540" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="6">
         <v>540</v>
       </c>
@@ -56386,7 +56401,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="541" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="6">
         <v>541</v>
       </c>
@@ -56463,7 +56478,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="542" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="6">
         <v>542</v>
       </c>
@@ -56540,7 +56555,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="543" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="6">
         <v>543</v>
       </c>
@@ -56617,7 +56632,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="544" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="6">
         <v>544</v>
       </c>
@@ -56694,7 +56709,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="545" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="6">
         <v>545</v>
       </c>
@@ -56771,7 +56786,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="546" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="6">
         <v>546</v>
       </c>
@@ -56848,7 +56863,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="547" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="6">
         <v>547</v>
       </c>
@@ -56925,7 +56940,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="548" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="6">
         <v>548</v>
       </c>
@@ -57002,7 +57017,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="549" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="6">
         <v>549</v>
       </c>
@@ -57079,7 +57094,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="550" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="6">
         <v>550</v>
       </c>
@@ -57156,7 +57171,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="551" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="6">
         <v>551</v>
       </c>
@@ -57233,7 +57248,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="552" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="6">
         <v>552</v>
       </c>
@@ -57310,7 +57325,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="553" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="6">
         <v>553</v>
       </c>
@@ -57387,7 +57402,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="554" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="6">
         <v>554</v>
       </c>
@@ -57464,7 +57479,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="555" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="6">
         <v>555</v>
       </c>
@@ -57541,7 +57556,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="556" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="6">
         <v>556</v>
       </c>
@@ -57618,7 +57633,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="557" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="6">
         <v>557</v>
       </c>
@@ -57695,7 +57710,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="558" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="6">
         <v>558</v>
       </c>
@@ -57772,7 +57787,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="559" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="6">
         <v>559</v>
       </c>
@@ -57849,7 +57864,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="560" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="6">
         <v>560</v>
       </c>
@@ -57926,7 +57941,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="561" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="6">
         <v>561</v>
       </c>
@@ -58003,7 +58018,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="562" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="6">
         <v>562</v>
       </c>
@@ -58080,7 +58095,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="563" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="6">
         <v>563</v>
       </c>
@@ -58157,7 +58172,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="564" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="6">
         <v>564</v>
       </c>
@@ -58234,7 +58249,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="565" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="6">
         <v>565</v>
       </c>
@@ -58311,7 +58326,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="566" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="6">
         <v>566</v>
       </c>
@@ -58388,7 +58403,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="567" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="6">
         <v>567</v>
       </c>
@@ -58465,7 +58480,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="568" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="6">
         <v>568</v>
       </c>
@@ -58542,7 +58557,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="569" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="6">
         <v>569</v>
       </c>
@@ -58619,7 +58634,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="570" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="6">
         <v>570</v>
       </c>
@@ -58696,7 +58711,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="571" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="6">
         <v>571</v>
       </c>
@@ -58773,7 +58788,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="572" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="6">
         <v>572</v>
       </c>
@@ -58850,7 +58865,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="573" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="6">
         <v>573</v>
       </c>
@@ -58927,7 +58942,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="574" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="6">
         <v>574</v>
       </c>
@@ -59004,7 +59019,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="575" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="6">
         <v>575</v>
       </c>
@@ -59081,7 +59096,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="576" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="6">
         <v>576</v>
       </c>
@@ -59158,7 +59173,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="577" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="6">
         <v>577</v>
       </c>
@@ -59235,7 +59250,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="578" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="6">
         <v>578</v>
       </c>
@@ -59312,7 +59327,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="579" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="6">
         <v>579</v>
       </c>
@@ -59389,7 +59404,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="580" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="6">
         <v>580</v>
       </c>
@@ -59466,7 +59481,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="581" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="6">
         <v>581</v>
       </c>
@@ -59543,7 +59558,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="582" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="6">
         <v>582</v>
       </c>
@@ -59620,7 +59635,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="583" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="6">
         <v>583</v>
       </c>
@@ -59697,7 +59712,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="584" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="6">
         <v>584</v>
       </c>
@@ -59774,7 +59789,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="585" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="6">
         <v>585</v>
       </c>
@@ -59851,7 +59866,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="586" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="6">
         <v>586</v>
       </c>
@@ -59928,7 +59943,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="587" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="6">
         <v>587</v>
       </c>
@@ -60005,7 +60020,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="588" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="6">
         <v>588</v>
       </c>
@@ -60082,7 +60097,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="589" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="6">
         <v>589</v>
       </c>
@@ -60159,7 +60174,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="590" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="6">
         <v>590</v>
       </c>
@@ -60236,7 +60251,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="591" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="6">
         <v>591</v>
       </c>
@@ -60313,7 +60328,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="592" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="6">
         <v>592</v>
       </c>
@@ -60390,7 +60405,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="593" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="6">
         <v>593</v>
       </c>
@@ -60467,7 +60482,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="594" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="6">
         <v>594</v>
       </c>
@@ -60544,7 +60559,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="595" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="6">
         <v>595</v>
       </c>
@@ -60621,7 +60636,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="596" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="6">
         <v>596</v>
       </c>
@@ -60698,7 +60713,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="597" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="6">
         <v>597</v>
       </c>
@@ -60775,7 +60790,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="598" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="6">
         <v>598</v>
       </c>
@@ -60852,7 +60867,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="599" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="6">
         <v>599</v>
       </c>
@@ -60929,7 +60944,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="600" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="6">
         <v>600</v>
       </c>
@@ -61006,7 +61021,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="601" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="6">
         <v>601</v>
       </c>
@@ -61083,7 +61098,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="602" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="6">
         <v>602</v>
       </c>
@@ -61160,7 +61175,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="603" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="6">
         <v>603</v>
       </c>
@@ -61237,7 +61252,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="604" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="6">
         <v>604</v>
       </c>
@@ -61314,7 +61329,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="605" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="6">
         <v>605</v>
       </c>
@@ -61391,7 +61406,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="606" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="6">
         <v>606</v>
       </c>
@@ -61468,7 +61483,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="607" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="6">
         <v>607</v>
       </c>
@@ -61545,7 +61560,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="608" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="6">
         <v>608</v>
       </c>
@@ -61622,7 +61637,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="609" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="6">
         <v>609</v>
       </c>
@@ -61699,7 +61714,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="610" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" s="6">
         <v>610</v>
       </c>
@@ -61776,7 +61791,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="611" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" s="6">
         <v>611</v>
       </c>
@@ -61853,7 +61868,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="612" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" s="6">
         <v>612</v>
       </c>
@@ -61930,7 +61945,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="613" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="6">
         <v>613</v>
       </c>
@@ -62007,7 +62022,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="614" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" s="6">
         <v>614</v>
       </c>
@@ -62084,7 +62099,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="615" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" s="6">
         <v>615</v>
       </c>
@@ -62161,7 +62176,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="616" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" s="6">
         <v>616</v>
       </c>
@@ -62238,7 +62253,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="617" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617" s="6">
         <v>617</v>
       </c>
@@ -62315,7 +62330,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="618" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618" s="6">
         <v>618</v>
       </c>
@@ -62392,7 +62407,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="619" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" s="6">
         <v>619</v>
       </c>
@@ -62469,7 +62484,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="620" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" s="6">
         <v>620</v>
       </c>
@@ -62546,7 +62561,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="621" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" s="6">
         <v>621</v>
       </c>
@@ -62623,7 +62638,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="622" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" s="6">
         <v>622</v>
       </c>
@@ -62700,7 +62715,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="623" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="6">
         <v>623</v>
       </c>
@@ -62777,7 +62792,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="624" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" s="6">
         <v>624</v>
       </c>
@@ -62854,7 +62869,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="625" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="6">
         <v>625</v>
       </c>
@@ -62931,7 +62946,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="626" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" s="6">
         <v>626</v>
       </c>
@@ -63008,7 +63023,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="627" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627" s="6">
         <v>627</v>
       </c>
@@ -63085,7 +63100,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="628" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A628" s="6">
         <v>628</v>
       </c>
@@ -63162,7 +63177,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="629" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A629" s="6">
         <v>629</v>
       </c>
@@ -63239,7 +63254,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="630" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A630" s="6">
         <v>630</v>
       </c>
@@ -63316,7 +63331,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="631" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631" s="6">
         <v>631</v>
       </c>
@@ -63393,7 +63408,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="632" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A632" s="6">
         <v>632</v>
       </c>
@@ -63470,7 +63485,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="633" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A633" s="6">
         <v>633</v>
       </c>
@@ -63547,7 +63562,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="634" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A634" s="6">
         <v>634</v>
       </c>
@@ -63624,7 +63639,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="635" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A635" s="6">
         <v>635</v>
       </c>
@@ -63701,7 +63716,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="636" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A636" s="6">
         <v>636</v>
       </c>
@@ -63778,7 +63793,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="637" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A637" s="6">
         <v>637</v>
       </c>
@@ -63855,7 +63870,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="638" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A638" s="6">
         <v>638</v>
       </c>
@@ -63932,7 +63947,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="639" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A639" s="6">
         <v>639</v>
       </c>
@@ -64009,7 +64024,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="640" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A640" s="6">
         <v>640</v>
       </c>
@@ -64086,7 +64101,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="641" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A641" s="6">
         <v>641</v>
       </c>
@@ -64163,7 +64178,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="642" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A642" s="6">
         <v>642</v>
       </c>
@@ -64240,7 +64255,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="643" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A643" s="6">
         <v>643</v>
       </c>
@@ -64317,7 +64332,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="644" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A644" s="6">
         <v>644</v>
       </c>
@@ -64394,7 +64409,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="645" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A645" s="6">
         <v>645</v>
       </c>
@@ -64471,7 +64486,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="646" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A646" s="6">
         <v>646</v>
       </c>
@@ -64548,7 +64563,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="647" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A647" s="6">
         <v>647</v>
       </c>
@@ -64625,7 +64640,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="648" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648" s="6">
         <v>648</v>
       </c>
@@ -64702,7 +64717,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="649" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649" s="6">
         <v>649</v>
       </c>
@@ -64779,7 +64794,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="650" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="6">
         <v>650</v>
       </c>
@@ -64856,7 +64871,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="651" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="6">
         <v>651</v>
       </c>
@@ -64933,7 +64948,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="652" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A652" s="6">
         <v>652</v>
       </c>
@@ -65010,7 +65025,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="653" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653" s="6">
         <v>653</v>
       </c>
@@ -65087,7 +65102,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="654" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A654" s="6">
         <v>654</v>
       </c>
@@ -65164,7 +65179,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="655" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A655" s="6">
         <v>655</v>
       </c>
@@ -65241,7 +65256,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="656" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A656" s="6">
         <v>656</v>
       </c>
@@ -65318,7 +65333,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="657" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A657" s="6">
         <v>657</v>
       </c>
@@ -65395,7 +65410,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="658" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A658" s="6">
         <v>658</v>
       </c>
@@ -65472,7 +65487,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="659" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A659" s="6">
         <v>659</v>
       </c>
@@ -65549,7 +65564,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="660" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A660" s="6">
         <v>660</v>
       </c>
@@ -65626,7 +65641,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="661" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A661" s="6">
         <v>661</v>
       </c>
@@ -65703,7 +65718,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="662" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A662" s="6">
         <v>662</v>
       </c>
@@ -65780,7 +65795,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="663" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A663" s="6">
         <v>663</v>
       </c>
@@ -65857,7 +65872,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="664" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A664" s="6">
         <v>664</v>
       </c>
@@ -65934,7 +65949,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="665" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A665" s="6">
         <v>665</v>
       </c>
@@ -66011,7 +66026,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="666" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A666" s="6">
         <v>666</v>
       </c>
@@ -66088,7 +66103,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="667" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A667" s="6">
         <v>667</v>
       </c>
@@ -66165,7 +66180,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="668" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A668" s="6">
         <v>668</v>
       </c>
@@ -66242,7 +66257,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="669" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A669" s="6">
         <v>669</v>
       </c>
@@ -66319,7 +66334,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="670" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A670" s="6">
         <v>670</v>
       </c>
@@ -66396,7 +66411,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="671" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A671" s="6">
         <v>671</v>
       </c>
@@ -66473,7 +66488,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="672" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A672" s="6">
         <v>672</v>
       </c>
@@ -66550,7 +66565,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="673" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A673" s="6">
         <v>673</v>
       </c>
@@ -66627,7 +66642,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="674" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A674" s="6">
         <v>674</v>
       </c>
@@ -66704,7 +66719,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="675" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A675" s="6">
         <v>675</v>
       </c>
@@ -66781,7 +66796,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="676" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A676" s="6">
         <v>676</v>
       </c>
@@ -66858,7 +66873,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="677" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A677" s="6">
         <v>677</v>
       </c>
@@ -66935,7 +66950,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="678" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A678" s="6">
         <v>678</v>
       </c>
@@ -67012,7 +67027,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="679" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A679" s="6">
         <v>679</v>
       </c>
@@ -67089,7 +67104,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="680" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A680" s="6">
         <v>680</v>
       </c>
@@ -67166,7 +67181,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="681" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A681" s="6">
         <v>681</v>
       </c>
@@ -67243,7 +67258,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="682" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A682" s="6">
         <v>682</v>
       </c>
@@ -67320,7 +67335,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="683" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A683" s="6">
         <v>683</v>
       </c>
@@ -67397,7 +67412,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="684" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A684" s="6">
         <v>684</v>
       </c>
@@ -67474,7 +67489,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="685" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A685" s="6">
         <v>685</v>
       </c>
@@ -67551,7 +67566,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="686" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A686" s="6">
         <v>686</v>
       </c>
@@ -67628,7 +67643,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="687" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A687" s="6">
         <v>687</v>
       </c>
@@ -67705,7 +67720,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="688" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A688" s="6">
         <v>688</v>
       </c>
@@ -67782,7 +67797,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="689" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A689" s="6">
         <v>689</v>
       </c>
@@ -67859,7 +67874,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="690" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A690" s="6">
         <v>690</v>
       </c>
@@ -67936,7 +67951,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="691" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A691" s="6">
         <v>691</v>
       </c>
@@ -68013,7 +68028,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="692" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A692" s="6">
         <v>692</v>
       </c>
@@ -68090,7 +68105,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="693" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A693" s="6">
         <v>693</v>
       </c>
@@ -68167,7 +68182,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="694" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A694" s="6">
         <v>694</v>
       </c>
@@ -68244,7 +68259,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="695" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A695" s="6">
         <v>695</v>
       </c>
@@ -68321,7 +68336,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="696" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A696" s="6">
         <v>696</v>
       </c>
@@ -68398,7 +68413,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="697" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A697" s="6">
         <v>697</v>
       </c>
@@ -68475,7 +68490,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="698" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A698" s="6">
         <v>698</v>
       </c>
@@ -68552,7 +68567,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="699" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A699" s="6">
         <v>699</v>
       </c>
@@ -68629,7 +68644,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="700" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A700" s="6">
         <v>700</v>
       </c>
@@ -68706,7 +68721,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="701" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A701" s="6">
         <v>701</v>
       </c>
@@ -68783,7 +68798,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="702" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A702" s="6">
         <v>702</v>
       </c>
@@ -68860,7 +68875,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="703" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703" s="6">
         <v>703</v>
       </c>
@@ -68937,7 +68952,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="704" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A704" s="6">
         <v>704</v>
       </c>
@@ -69014,7 +69029,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="705" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A705" s="6">
         <v>705</v>
       </c>
@@ -69091,7 +69106,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="706" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A706" s="6">
         <v>706</v>
       </c>
@@ -69168,7 +69183,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="707" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A707" s="6">
         <v>707</v>
       </c>
@@ -69245,7 +69260,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="708" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A708" s="6">
         <v>708</v>
       </c>
@@ -69322,7 +69337,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="709" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="6">
         <v>709</v>
       </c>
@@ -69399,7 +69414,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="710" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="6">
         <v>710</v>
       </c>
@@ -69476,7 +69491,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="711" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="6">
         <v>711</v>
       </c>
@@ -69553,7 +69568,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="712" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A712" s="6">
         <v>712</v>
       </c>
@@ -69630,7 +69645,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="713" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A713" s="6">
         <v>713</v>
       </c>
@@ -69707,7 +69722,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="714" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A714" s="6">
         <v>714</v>
       </c>
@@ -69784,7 +69799,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="715" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A715" s="6">
         <v>715</v>
       </c>
@@ -69861,7 +69876,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="716" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A716" s="6">
         <v>716</v>
       </c>
@@ -69938,7 +69953,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="717" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A717" s="6">
         <v>717</v>
       </c>
@@ -70015,7 +70030,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="718" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A718" s="6">
         <v>718</v>
       </c>
@@ -70092,7 +70107,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="719" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A719" s="6">
         <v>719</v>
       </c>
@@ -70169,7 +70184,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="720" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A720" s="6">
         <v>720</v>
       </c>
@@ -70246,7 +70261,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="721" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A721" s="6">
         <v>721</v>
       </c>
@@ -70323,7 +70338,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="722" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A722" s="6">
         <v>722</v>
       </c>
